--- a/education_forms/006_child_consultation_registration_form--education_forms.xlsx
+++ b/education_forms/006_child_consultation_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -893,8 +893,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -922,12 +922,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'parent',_'value':_'parent'}</t>
+          <t>parent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Parent', 'value': 'parent'}</t>
+          <t>Parent</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'legal_guardian',_'value':_'guardian'}</t>
+          <t>legal_guardian</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Legal Guardian', 'value': 'guardian'}</t>
+          <t>Legal Guardian</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'grandparent',_'value':_'grandparent'}</t>
+          <t>grandparent</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Grandparent', 'value': 'grandparent'}</t>
+          <t>Grandparent</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'academic_progress',_'value':_'academic'}</t>
+          <t>academic_progress</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Academic Progress', 'value': 'academic'}</t>
+          <t>Academic Progress</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'emotional_well-being',_'value':_'emotional'}</t>
+          <t>emotional_well-being</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Emotional Well-being', 'value': 'emotional'}</t>
+          <t>Emotional Well-being</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'social_interactions',_'value':_'social'}</t>
+          <t>social_interactions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Social Interactions', 'value': 'social'}</t>
+          <t>Social Interactions</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'speech_and_language',_'value':_'speech'}</t>
+          <t>speech_and_language</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Speech and Language', 'value': 'speech'}</t>
+          <t>Speech and Language</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
